--- a/templates_excel/人员专属工作日历.xlsx
+++ b/templates_excel/人员专属工作日历.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>holiday</t>
+          <t>假期</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
@@ -538,12 +538,12 @@
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>否</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>否</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>holiday</t>
+          <t>假期</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
@@ -582,12 +582,12 @@
       <c r="G3" s="6" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>是</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>是</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -5072,13 +5072,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="C2:C500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
-      <formula1>"workday,holiday"</formula1>
+      <formula1>"工作日,假期"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
-      <formula1>"yes,no"</formula1>
+      <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I500" showErrorMessage="1" showInputMessage="1" allowBlank="1" type="list">
-      <formula1>"yes,no"</formula1>
+      <formula1>"是,否"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
